--- a/public/docs/ImportKategoriTemplate.xlsx
+++ b/public/docs/ImportKategoriTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahwal\Documents\Template Exel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fauza\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3EFB24-179F-41AF-9025-DB6B4E9CF374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942ADF97-3612-4D4A-946A-D27E1CADD091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="405" windowWidth="20400" windowHeight="11835" xr2:uid="{B3D6D4D0-35A3-49F9-8268-AA86B970F7A6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B3D6D4D0-35A3-49F9-8268-AA86B970F7A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Import Kategori" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>non_medis</t>
   </si>
@@ -61,9 +61,6 @@
     <t>nama tabel</t>
   </si>
   <si>
-    <t>peralatan IT</t>
-  </si>
-  <si>
     <t>komputer ,mouse</t>
   </si>
   <si>
@@ -82,40 +79,26 @@
     <t>*Wajib Diisi : Hanya menerima 'medis' atau 'non_medis'</t>
   </si>
   <si>
-    <t>*Wajib Diisi :  data wajib sama dengan di menu kategori</t>
-  </si>
-  <si>
     <t>*Nama Kategori</t>
   </si>
   <si>
     <t>NOTE :BUKA BATAS PENGISIAN</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>*Wajib Diisi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -126,13 +109,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="18"/>
-      <color theme="0"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <sz val="11"/>
@@ -140,6 +116,34 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -211,38 +215,38 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -560,43 +564,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC2458E7-D575-403C-96EF-16FEDBED62D5}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="5" max="5" width="34.5703125" customWidth="1"/>
+    <col min="5" max="5" width="34.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -609,74 +613,76 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="91.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
+    <col min="4" max="4" width="91.6640625" customWidth="1"/>
+    <col min="5" max="5" width="31.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="B4" s="6">
         <v>100</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="B5" s="6">
         <v>1000</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D5" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
